--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/73.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/73.xlsx
@@ -426,13 +426,13 @@
         <v>-0.7287264574052702</v>
       </c>
       <c r="E2">
-        <v>-9.818489980496217</v>
+        <v>0.3966922463643213</v>
       </c>
       <c r="F2">
-        <v>-4.407765463463552</v>
+        <v>-2.200434726041377</v>
       </c>
       <c r="G2">
-        <v>-13.83747622031429</v>
+        <v>-8.630300651284001</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.58150018561866</v>
       </c>
       <c r="E3">
-        <v>-9.81415170239687</v>
+        <v>-0.006962341257391305</v>
       </c>
       <c r="F3">
-        <v>-4.488397089717251</v>
+        <v>-2.047813830647388</v>
       </c>
       <c r="G3">
-        <v>-14.41537808624993</v>
+        <v>-7.972773381765315</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.5068949200512797</v>
       </c>
       <c r="E4">
-        <v>-10.92799781169351</v>
+        <v>-0.5926434700914216</v>
       </c>
       <c r="F4">
-        <v>-4.036736390280043</v>
+        <v>-2.249529576903095</v>
       </c>
       <c r="G4">
-        <v>-14.20019229515998</v>
+        <v>-7.882493851778754</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.4938248494350604</v>
       </c>
       <c r="E5">
-        <v>-11.3452197074422</v>
+        <v>-2.092786526138373</v>
       </c>
       <c r="F5">
-        <v>-4.251165919433918</v>
+        <v>-2.093204222483787</v>
       </c>
       <c r="G5">
-        <v>-14.05860102242683</v>
+        <v>-7.19244967660597</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.4975359288726729</v>
       </c>
       <c r="E6">
-        <v>-11.56140452809438</v>
+        <v>-3.468749767946989</v>
       </c>
       <c r="F6">
-        <v>-3.955230008048988</v>
+        <v>-2.126773811482237</v>
       </c>
       <c r="G6">
-        <v>-13.8810196710189</v>
+        <v>-7.64355201659843</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.4813093163667613</v>
       </c>
       <c r="E7">
-        <v>-12.18728039222049</v>
+        <v>-3.984887121445225</v>
       </c>
       <c r="F7">
-        <v>-3.990396689400036</v>
+        <v>-1.553125243206565</v>
       </c>
       <c r="G7">
-        <v>-13.92278469963829</v>
+        <v>-6.852485592053463</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.409829331322359</v>
       </c>
       <c r="E8">
-        <v>-12.75542274122281</v>
+        <v>-3.327225898259274</v>
       </c>
       <c r="F8">
-        <v>-3.60530773628881</v>
+        <v>-1.850766763073858</v>
       </c>
       <c r="G8">
-        <v>-13.89886623508072</v>
+        <v>-6.829172512873608</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.2567923050387989</v>
       </c>
       <c r="E9">
-        <v>-12.96242381658743</v>
+        <v>-4.34853264120917</v>
       </c>
       <c r="F9">
-        <v>-3.665733824853423</v>
+        <v>-1.759049095868494</v>
       </c>
       <c r="G9">
-        <v>-13.69672329968957</v>
+        <v>-7.411198874309472</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.00606234168163762</v>
       </c>
       <c r="E10">
-        <v>-13.67843442736222</v>
+        <v>-4.823420124971538</v>
       </c>
       <c r="F10">
-        <v>-3.79715017147055</v>
+        <v>-1.813141487271302</v>
       </c>
       <c r="G10">
-        <v>-13.81137738403046</v>
+        <v>-6.429647694574061</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.3441443753903339</v>
       </c>
       <c r="E11">
-        <v>-13.62054694412217</v>
+        <v>-6.479048336071851</v>
       </c>
       <c r="F11">
-        <v>-3.628176475177896</v>
+        <v>-1.537874170953623</v>
       </c>
       <c r="G11">
-        <v>-13.20021213453595</v>
+        <v>-5.583286124309331</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.7814574892531229</v>
       </c>
       <c r="E12">
-        <v>-15.20599739352561</v>
+        <v>-7.145055536853938</v>
       </c>
       <c r="F12">
-        <v>-3.169168985245259</v>
+        <v>-1.527538630868894</v>
       </c>
       <c r="G12">
-        <v>-12.83357171870516</v>
+        <v>-5.722180232920626</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.278389484845699</v>
       </c>
       <c r="E13">
-        <v>-15.2815595108176</v>
+        <v>-7.278129274043339</v>
       </c>
       <c r="F13">
-        <v>-3.017942232190181</v>
+        <v>-1.032986724049533</v>
       </c>
       <c r="G13">
-        <v>-12.31897117909432</v>
+        <v>-5.096759716361106</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.798889495362646</v>
       </c>
       <c r="E14">
-        <v>-16.1099894888328</v>
+        <v>-8.721616591780327</v>
       </c>
       <c r="F14">
-        <v>-2.950160241088709</v>
+        <v>-0.8240111658756908</v>
       </c>
       <c r="G14">
-        <v>-12.25953185054498</v>
+        <v>-4.755972045197178</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.303360831881683</v>
       </c>
       <c r="E15">
-        <v>-16.65947452492352</v>
+        <v>-9.604940731716507</v>
       </c>
       <c r="F15">
-        <v>-2.301277688555981</v>
+        <v>-0.7033486848817064</v>
       </c>
       <c r="G15">
-        <v>-12.07392299059187</v>
+        <v>-4.215787821087354</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.754434023566573</v>
       </c>
       <c r="E16">
-        <v>-17.03957651923134</v>
+        <v>-9.465509017020336</v>
       </c>
       <c r="F16">
-        <v>-2.767146545686006</v>
+        <v>-0.3976943671271336</v>
       </c>
       <c r="G16">
-        <v>-11.38260570145403</v>
+        <v>-3.493771423039342</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.120023772873347</v>
       </c>
       <c r="E17">
-        <v>-17.80437690896476</v>
+        <v>-10.92312064518725</v>
       </c>
       <c r="F17">
-        <v>-2.314753569464723</v>
+        <v>0.006056875201762233</v>
       </c>
       <c r="G17">
-        <v>-11.04022663783377</v>
+        <v>-2.54584292062356</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.374408916693994</v>
       </c>
       <c r="E18">
-        <v>-18.59133512201772</v>
+        <v>-11.92761769262067</v>
       </c>
       <c r="F18">
-        <v>-1.679913501144252</v>
+        <v>0.07644242505023342</v>
       </c>
       <c r="G18">
-        <v>-10.83137032313199</v>
+        <v>-3.254901774733326</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.500044668904816</v>
       </c>
       <c r="E19">
-        <v>-19.73442611645589</v>
+        <v>-13.24796221666708</v>
       </c>
       <c r="F19">
-        <v>-1.716889336903013</v>
+        <v>0.5424661868845821</v>
       </c>
       <c r="G19">
-        <v>-10.28629051645548</v>
+        <v>-2.124947506307349</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.490298606502547</v>
       </c>
       <c r="E20">
-        <v>-20.11327825193759</v>
+        <v>-13.74156135502914</v>
       </c>
       <c r="F20">
-        <v>-1.144031031129612</v>
+        <v>0.7734473251137934</v>
       </c>
       <c r="G20">
-        <v>-10.64545959079542</v>
+        <v>-2.26220756658204</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.351542761898815</v>
       </c>
       <c r="E21">
-        <v>-20.55909293257072</v>
+        <v>-14.33763986018478</v>
       </c>
       <c r="F21">
-        <v>-0.8057622319920177</v>
+        <v>1.065551208893372</v>
       </c>
       <c r="G21">
-        <v>-9.37621746717101</v>
+        <v>-2.528898692490588</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.104956757777678</v>
       </c>
       <c r="E22">
-        <v>-20.95390793892946</v>
+        <v>-14.90723584934357</v>
       </c>
       <c r="F22">
-        <v>-0.9505699660428021</v>
+        <v>1.079583752696796</v>
       </c>
       <c r="G22">
-        <v>-10.11365560654841</v>
+        <v>-2.483647365964286</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.784291733999382</v>
       </c>
       <c r="E23">
-        <v>-21.66318923732884</v>
+        <v>-16.26917440715043</v>
       </c>
       <c r="F23">
-        <v>-0.8622891951916531</v>
+        <v>1.405246456698588</v>
       </c>
       <c r="G23">
-        <v>-9.58965436716977</v>
+        <v>-2.619762279914731</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.432204370771686</v>
       </c>
       <c r="E24">
-        <v>-22.13038737222618</v>
+        <v>-17.02117732933818</v>
       </c>
       <c r="F24">
-        <v>-0.8363869748735154</v>
+        <v>1.534213320905637</v>
       </c>
       <c r="G24">
-        <v>-10.30083617162849</v>
+        <v>-2.370779906762507</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.093853204541947</v>
       </c>
       <c r="E25">
-        <v>-21.78321644090214</v>
+        <v>-15.53065728055752</v>
       </c>
       <c r="F25">
-        <v>-0.7761522391789494</v>
+        <v>1.694959672153687</v>
       </c>
       <c r="G25">
-        <v>-9.641215482754884</v>
+        <v>-1.456949858792475</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.811164847096992</v>
       </c>
       <c r="E26">
-        <v>-21.94207530909122</v>
+        <v>-16.03038344425196</v>
       </c>
       <c r="F26">
-        <v>-0.9194250084323462</v>
+        <v>2.180618226536592</v>
       </c>
       <c r="G26">
-        <v>-10.20663886309996</v>
+        <v>-1.509574090162849</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.617389455261605</v>
       </c>
       <c r="E27">
-        <v>-21.37221213996598</v>
+        <v>-16.77337923163845</v>
       </c>
       <c r="F27">
-        <v>-0.902399573202608</v>
+        <v>1.600981390306083</v>
       </c>
       <c r="G27">
-        <v>-10.09947088574693</v>
+        <v>-2.320229407417701</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.531730378708249</v>
       </c>
       <c r="E28">
-        <v>-21.82153638795505</v>
+        <v>-17.16179097575035</v>
       </c>
       <c r="F28">
-        <v>-0.9241616132415538</v>
+        <v>1.874567949163481</v>
       </c>
       <c r="G28">
-        <v>-9.746395039842884</v>
+        <v>-3.031224182247539</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.559471601757814</v>
       </c>
       <c r="E29">
-        <v>-21.92213643803545</v>
+        <v>-15.56386458045577</v>
       </c>
       <c r="F29">
-        <v>-1.097768368418066</v>
+        <v>1.900007112103454</v>
       </c>
       <c r="G29">
-        <v>-10.01489740005225</v>
+        <v>-3.015231508366805</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.689844397805379</v>
       </c>
       <c r="E30">
-        <v>-21.99624944364498</v>
+        <v>-14.45967317774348</v>
       </c>
       <c r="F30">
-        <v>-1.159947282407002</v>
+        <v>1.570976266241879</v>
       </c>
       <c r="G30">
-        <v>-9.698538423398382</v>
+        <v>-3.145187569450173</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.898456566895049</v>
       </c>
       <c r="E31">
-        <v>-21.55641687717599</v>
+        <v>-15.97918451712124</v>
       </c>
       <c r="F31">
-        <v>-1.238520415664744</v>
+        <v>1.493699527969519</v>
       </c>
       <c r="G31">
-        <v>-10.30750033261573</v>
+        <v>-2.82469425363141</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.151809529393073</v>
       </c>
       <c r="E32">
-        <v>-21.717594324057</v>
+        <v>-14.14329134119759</v>
       </c>
       <c r="F32">
-        <v>-1.421526655760822</v>
+        <v>1.225227309457005</v>
       </c>
       <c r="G32">
-        <v>-9.837448938117475</v>
+        <v>-1.853255798742208</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.410463508985042</v>
       </c>
       <c r="E33">
-        <v>-20.54900349248163</v>
+        <v>-14.99867932498045</v>
       </c>
       <c r="F33">
-        <v>-1.176593325366258</v>
+        <v>1.250885161391317</v>
       </c>
       <c r="G33">
-        <v>-9.926534103456399</v>
+        <v>-2.38328792334711</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.634897746048097</v>
       </c>
       <c r="E34">
-        <v>-21.0213550307997</v>
+        <v>-14.23626996952308</v>
       </c>
       <c r="F34">
-        <v>-1.168235926639414</v>
+        <v>1.617142838334701</v>
       </c>
       <c r="G34">
-        <v>-9.678057038424329</v>
+        <v>-2.321167836783702</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.787943760593028</v>
       </c>
       <c r="E35">
-        <v>-20.45704377080787</v>
+        <v>-14.47221705074473</v>
       </c>
       <c r="F35">
-        <v>-1.310727545431971</v>
+        <v>1.44064259582021</v>
       </c>
       <c r="G35">
-        <v>-9.775112290931144</v>
+        <v>-2.016171730390197</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.839680272648097</v>
       </c>
       <c r="E36">
-        <v>-19.73080786572377</v>
+        <v>-13.27970681946085</v>
       </c>
       <c r="F36">
-        <v>-1.154151195689614</v>
+        <v>1.52495548681195</v>
       </c>
       <c r="G36">
-        <v>-9.802891112653404</v>
+        <v>-1.864402108379641</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.772341164842548</v>
       </c>
       <c r="E37">
-        <v>-19.48206784543045</v>
+        <v>-14.12073954063939</v>
       </c>
       <c r="F37">
-        <v>-1.456295720758525</v>
+        <v>1.375814562877121</v>
       </c>
       <c r="G37">
-        <v>-9.630909165836668</v>
+        <v>-1.806370423879302</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.582186351206039</v>
       </c>
       <c r="E38">
-        <v>-20.07304728885345</v>
+        <v>-13.40391833301724</v>
       </c>
       <c r="F38">
-        <v>-0.9532911529609984</v>
+        <v>1.383742038921912</v>
       </c>
       <c r="G38">
-        <v>-9.639276280813252</v>
+        <v>-2.382759646676039</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.280083060431533</v>
       </c>
       <c r="E39">
-        <v>-19.24689966173812</v>
+        <v>-13.06123059096079</v>
       </c>
       <c r="F39">
-        <v>-1.264364650264685</v>
+        <v>1.435639256707302</v>
       </c>
       <c r="G39">
-        <v>-9.35967682928985</v>
+        <v>-1.702605073283422</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.889325203003506</v>
       </c>
       <c r="E40">
-        <v>-19.04228056370153</v>
+        <v>-11.50457670777212</v>
       </c>
       <c r="F40">
-        <v>-1.040792430086113</v>
+        <v>1.615671657827329</v>
       </c>
       <c r="G40">
-        <v>-9.577996186969063</v>
+        <v>-1.389464974979375</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.441448572757646</v>
       </c>
       <c r="E41">
-        <v>-18.21263242617827</v>
+        <v>-11.17737634682191</v>
       </c>
       <c r="F41">
-        <v>-1.068031635392369</v>
+        <v>1.514261263641808</v>
       </c>
       <c r="G41">
-        <v>-9.261279557165221</v>
+        <v>-1.618313772642847</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.9695758576052127</v>
       </c>
       <c r="E42">
-        <v>-18.53560319240532</v>
+        <v>-12.34195947890049</v>
       </c>
       <c r="F42">
-        <v>-1.183509364812231</v>
+        <v>1.336241795310583</v>
       </c>
       <c r="G42">
-        <v>-9.180860097964789</v>
+        <v>-1.429308848375713</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5029305537898899</v>
       </c>
       <c r="E43">
-        <v>-18.46658019158041</v>
+        <v>-10.47228841535363</v>
       </c>
       <c r="F43">
-        <v>-1.127904374531912</v>
+        <v>1.531050614161749</v>
       </c>
       <c r="G43">
-        <v>-8.995211863352967</v>
+        <v>-0.726166036737626</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.06370524209088954</v>
       </c>
       <c r="E44">
-        <v>-17.56180014179589</v>
+        <v>-9.795838553509851</v>
       </c>
       <c r="F44">
-        <v>-1.376553761095434</v>
+        <v>1.013915755207268</v>
       </c>
       <c r="G44">
-        <v>-8.924593412950598</v>
+        <v>-0.5999669743398228</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.3341942031853803</v>
       </c>
       <c r="E45">
-        <v>-17.47930040232415</v>
+        <v>-10.52364583907461</v>
       </c>
       <c r="F45">
-        <v>-1.368535164636335</v>
+        <v>1.294874783949581</v>
       </c>
       <c r="G45">
-        <v>-8.730515720152562</v>
+        <v>-1.231618530640728</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6851141374913555</v>
       </c>
       <c r="E46">
-        <v>-17.10857234921221</v>
+        <v>-9.890288935887831</v>
       </c>
       <c r="F46">
-        <v>-1.427874435168474</v>
+        <v>1.420379072412929</v>
       </c>
       <c r="G46">
-        <v>-8.880290359454976</v>
+        <v>-1.252542880525307</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.9903667340950506</v>
       </c>
       <c r="E47">
-        <v>-16.46720004703185</v>
+        <v>-9.700414549220222</v>
       </c>
       <c r="F47">
-        <v>-1.390012246288717</v>
+        <v>1.179824492109564</v>
       </c>
       <c r="G47">
-        <v>-8.620660422342354</v>
+        <v>-0.9420113533610184</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.254680258935029</v>
       </c>
       <c r="E48">
-        <v>-16.44160058346649</v>
+        <v>-8.472093145483683</v>
       </c>
       <c r="F48">
-        <v>-1.638246620783437</v>
+        <v>1.155187188815501</v>
       </c>
       <c r="G48">
-        <v>-8.180386113496061</v>
+        <v>-1.003468633169418</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.482237284549703</v>
       </c>
       <c r="E49">
-        <v>-15.70054298295527</v>
+        <v>-9.424385944556683</v>
       </c>
       <c r="F49">
-        <v>-1.592076735221004</v>
+        <v>0.776903273918273</v>
       </c>
       <c r="G49">
-        <v>-8.604392125850627</v>
+        <v>-0.8397553646824832</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.67573969240882</v>
       </c>
       <c r="E50">
-        <v>-15.35300977371062</v>
+        <v>-8.062003596297071</v>
       </c>
       <c r="F50">
-        <v>-1.302725516320928</v>
+        <v>0.9458222979623425</v>
       </c>
       <c r="G50">
-        <v>-8.511320276316978</v>
+        <v>-0.4539427712798547</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.837556869181269</v>
       </c>
       <c r="E51">
-        <v>-15.17040811629933</v>
+        <v>-6.43037629743741</v>
       </c>
       <c r="F51">
-        <v>-1.454701941875539</v>
+        <v>0.9368924973601639</v>
       </c>
       <c r="G51">
-        <v>-8.481241318281548</v>
+        <v>-1.357266347816544</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.969719955265959</v>
       </c>
       <c r="E52">
-        <v>-14.00527251039182</v>
+        <v>-8.079388408012516</v>
       </c>
       <c r="F52">
-        <v>-1.503130785345407</v>
+        <v>1.005143344411621</v>
       </c>
       <c r="G52">
-        <v>-8.714608358032374</v>
+        <v>0.143485644156042</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.072370472743436</v>
       </c>
       <c r="E53">
-        <v>-14.35583979722161</v>
+        <v>-6.91425733057901</v>
       </c>
       <c r="F53">
-        <v>-1.780855867747191</v>
+        <v>0.9402457286066963</v>
       </c>
       <c r="G53">
-        <v>-8.247900528303196</v>
+        <v>-0.7498466127321386</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.14411603456123</v>
       </c>
       <c r="E54">
-        <v>-13.29221446467003</v>
+        <v>-6.88333238158063</v>
       </c>
       <c r="F54">
-        <v>-1.89457497317091</v>
+        <v>0.6870966503111674</v>
       </c>
       <c r="G54">
-        <v>-8.505453452168689</v>
+        <v>-0.3637944901556705</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.182086677700839</v>
       </c>
       <c r="E55">
-        <v>-13.19800409141446</v>
+        <v>-5.963481570298581</v>
       </c>
       <c r="F55">
-        <v>-1.719763771790728</v>
+        <v>0.8972286093793179</v>
       </c>
       <c r="G55">
-        <v>-8.572541308173097</v>
+        <v>-1.136899507884237</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.181710738130077</v>
       </c>
       <c r="E56">
-        <v>-13.35000684995592</v>
+        <v>-5.964781242338782</v>
       </c>
       <c r="F56">
-        <v>-1.864290689291963</v>
+        <v>0.8271536973068966</v>
       </c>
       <c r="G56">
-        <v>-8.525278592830855</v>
+        <v>-0.8351780606070578</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.13840599845404</v>
       </c>
       <c r="E57">
-        <v>-12.46870693790117</v>
+        <v>-5.817501682187319</v>
       </c>
       <c r="F57">
-        <v>-1.635121190572674</v>
+        <v>0.9437530361901494</v>
       </c>
       <c r="G57">
-        <v>-8.899984251254763</v>
+        <v>-1.532102957389996</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.049446459625295</v>
       </c>
       <c r="E58">
-        <v>-12.35507846810071</v>
+        <v>-4.99799279796723</v>
       </c>
       <c r="F58">
-        <v>-1.846265414607046</v>
+        <v>0.828556951687239</v>
       </c>
       <c r="G58">
-        <v>-8.761227953948964</v>
+        <v>-0.9165425116166085</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.915514259374783</v>
       </c>
       <c r="E59">
-        <v>-12.97572847322197</v>
+        <v>-4.976989735519655</v>
       </c>
       <c r="F59">
-        <v>-1.558671162968308</v>
+        <v>1.206935300468386</v>
       </c>
       <c r="G59">
-        <v>-9.239554589220138</v>
+        <v>-1.447519628030631</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.741054192281184</v>
       </c>
       <c r="E60">
-        <v>-11.78111250152452</v>
+        <v>-4.124672057113994</v>
       </c>
       <c r="F60">
-        <v>-1.719565791981459</v>
+        <v>0.8567115029735886</v>
       </c>
       <c r="G60">
-        <v>-9.354331719369513</v>
+        <v>-1.642647311727689</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.53297574937941</v>
       </c>
       <c r="E61">
-        <v>-11.67794933515578</v>
+        <v>-3.352186846989553</v>
       </c>
       <c r="F61">
-        <v>-1.462088494006302</v>
+        <v>0.9145017264624933</v>
       </c>
       <c r="G61">
-        <v>-9.3300605234943</v>
+        <v>-2.157005040943124</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.299910375662688</v>
       </c>
       <c r="E62">
-        <v>-11.59525939977572</v>
+        <v>-3.633540937086113</v>
       </c>
       <c r="F62">
-        <v>-1.953785018388213</v>
+        <v>1.068415703372253</v>
       </c>
       <c r="G62">
-        <v>-9.341042772053763</v>
+        <v>-2.469078742240351</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.05251993046994</v>
       </c>
       <c r="E63">
-        <v>-11.41261245762435</v>
+        <v>-3.084327609435852</v>
       </c>
       <c r="F63">
-        <v>-1.924921384605067</v>
+        <v>0.9756269571150687</v>
       </c>
       <c r="G63">
-        <v>-9.624858593281052</v>
+        <v>-2.622265851964587</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.8013677184114821</v>
       </c>
       <c r="E64">
-        <v>-11.33429249966169</v>
+        <v>-3.125314827679276</v>
       </c>
       <c r="F64">
-        <v>-1.883062323006803</v>
+        <v>0.9978918161675139</v>
       </c>
       <c r="G64">
-        <v>-9.921602427452553</v>
+        <v>-2.406138350287083</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.5557610192368159</v>
       </c>
       <c r="E65">
-        <v>-11.33114973870037</v>
+        <v>-4.353061115216841</v>
       </c>
       <c r="F65">
-        <v>-1.707599196480617</v>
+        <v>1.102277706063891</v>
       </c>
       <c r="G65">
-        <v>-9.804039540199209</v>
+        <v>-3.02075708547291</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3237531175768703</v>
       </c>
       <c r="E66">
-        <v>-11.43498311922224</v>
+        <v>-3.629478895901233</v>
       </c>
       <c r="F66">
-        <v>-1.825211628697494</v>
+        <v>0.8129770175753859</v>
       </c>
       <c r="G66">
-        <v>-10.03521800516989</v>
+        <v>-2.710848990404916</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1123528450426059</v>
       </c>
       <c r="E67">
-        <v>-10.90185040277322</v>
+        <v>-3.335549233485373</v>
       </c>
       <c r="F67">
-        <v>-1.812494532329716</v>
+        <v>0.9681865611031236</v>
       </c>
       <c r="G67">
-        <v>-10.08447898444183</v>
+        <v>-2.517401292146293</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.07293206939935198</v>
       </c>
       <c r="E68">
-        <v>-11.38638353617193</v>
+        <v>-3.675565175877294</v>
       </c>
       <c r="F68">
-        <v>-1.84819302555336</v>
+        <v>0.9469058025252043</v>
       </c>
       <c r="G68">
-        <v>-9.87836577096375</v>
+        <v>-3.256102701824082</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.2284571475814991</v>
       </c>
       <c r="E69">
-        <v>-10.79874610656658</v>
+        <v>-2.112675583980062</v>
       </c>
       <c r="F69">
-        <v>-1.952981502007498</v>
+        <v>0.8445278752132134</v>
       </c>
       <c r="G69">
-        <v>-10.13086889484926</v>
+        <v>-3.45507597718881</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.3512877747808767</v>
       </c>
       <c r="E70">
-        <v>-11.48728699401084</v>
+        <v>-2.26919775958118</v>
       </c>
       <c r="F70">
-        <v>-1.849826566071681</v>
+        <v>0.8206592968689485</v>
       </c>
       <c r="G70">
-        <v>-10.25598515413245</v>
+        <v>-3.410559644291824</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.4397289248540089</v>
       </c>
       <c r="E71">
-        <v>-11.63332122381019</v>
+        <v>-2.960134209775492</v>
       </c>
       <c r="F71">
-        <v>-1.907068410339932</v>
+        <v>0.5121206038178278</v>
       </c>
       <c r="G71">
-        <v>-9.645182479620253</v>
+        <v>-3.366233622245285</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.4918950310411596</v>
       </c>
       <c r="E72">
-        <v>-11.39631900814475</v>
+        <v>-2.791656862794124</v>
       </c>
       <c r="F72">
-        <v>-2.095803639393772</v>
+        <v>0.364067326282875</v>
       </c>
       <c r="G72">
-        <v>-9.475064266649282</v>
+        <v>-3.235158664610147</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.5057769811485557</v>
       </c>
       <c r="E73">
-        <v>-10.99416334541958</v>
+        <v>-2.586788698687117</v>
       </c>
       <c r="F73">
-        <v>-1.941089459572908</v>
+        <v>0.8792712608214303</v>
       </c>
       <c r="G73">
-        <v>-9.753800756902551</v>
+        <v>-3.185887841673525</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.4805075316358798</v>
       </c>
       <c r="E74">
-        <v>-11.1203990868574</v>
+        <v>-2.881547071846381</v>
       </c>
       <c r="F74">
-        <v>-2.14791374760168</v>
+        <v>0.4110001382232866</v>
       </c>
       <c r="G74">
-        <v>-9.566662847702741</v>
+        <v>-3.582144563299866</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.4171379854204982</v>
       </c>
       <c r="E75">
-        <v>-11.67225704332814</v>
+        <v>-3.270081084756482</v>
       </c>
       <c r="F75">
-        <v>-1.967650231976271</v>
+        <v>0.3764340232392688</v>
       </c>
       <c r="G75">
-        <v>-9.252410415290042</v>
+        <v>-2.3597123464425</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.3212260307584466</v>
       </c>
       <c r="E76">
-        <v>-10.98040584138428</v>
+        <v>-4.230620234997449</v>
       </c>
       <c r="F76">
-        <v>-1.957892063971293</v>
+        <v>0.1405895399882215</v>
       </c>
       <c r="G76">
-        <v>-9.476987062483117</v>
+        <v>-2.077694634629786</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.2021692882201625</v>
       </c>
       <c r="E77">
-        <v>-11.79797653872908</v>
+        <v>-4.054657320481402</v>
       </c>
       <c r="F77">
-        <v>-2.25786046787305</v>
+        <v>0.6716923300887078</v>
       </c>
       <c r="G77">
-        <v>-9.202145382220907</v>
+        <v>-2.693008988786215</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.07094229799503028</v>
       </c>
       <c r="E78">
-        <v>-12.36131417680927</v>
+        <v>-3.008942102630163</v>
       </c>
       <c r="F78">
-        <v>-2.271786980648915</v>
+        <v>0.111628987218948</v>
       </c>
       <c r="G78">
-        <v>-9.1407373207359</v>
+        <v>-2.145556858922221</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.0616672139947318</v>
       </c>
       <c r="E79">
-        <v>-12.10139335419101</v>
+        <v>-4.645079761601464</v>
       </c>
       <c r="F79">
-        <v>-2.396860518062807</v>
+        <v>0.1495441916124842</v>
       </c>
       <c r="G79">
-        <v>-8.989240040114778</v>
+        <v>-1.640698266121379</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1861106217962113</v>
       </c>
       <c r="E80">
-        <v>-12.99526431009106</v>
+        <v>-5.623610539074905</v>
       </c>
       <c r="F80">
-        <v>-2.431979154104492</v>
+        <v>-0.04160572842051572</v>
       </c>
       <c r="G80">
-        <v>-9.398677428745408</v>
+        <v>-2.186555722307483</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.2946273819875023</v>
       </c>
       <c r="E81">
-        <v>-13.21564249767434</v>
+        <v>-5.506567599872657</v>
       </c>
       <c r="F81">
-        <v>-2.473097655244654</v>
+        <v>-0.05414969600110863</v>
       </c>
       <c r="G81">
-        <v>-8.788990369563427</v>
+        <v>-1.756896165205995</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.3825337859353617</v>
       </c>
       <c r="E82">
-        <v>-14.28008295554729</v>
+        <v>-6.770673005217806</v>
       </c>
       <c r="F82">
-        <v>-2.471397845334109</v>
+        <v>0.008343997600891669</v>
       </c>
       <c r="G82">
-        <v>-8.939519689824513</v>
+        <v>-0.9972408746495918</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.4488940337799927</v>
       </c>
       <c r="E83">
-        <v>-14.27519220361901</v>
+        <v>-7.290002932891451</v>
       </c>
       <c r="F83">
-        <v>-2.555981612466564</v>
+        <v>-0.1522433071058205</v>
       </c>
       <c r="G83">
-        <v>-8.437528884666625</v>
+        <v>-2.128950596609871</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.4966118885878683</v>
       </c>
       <c r="E84">
-        <v>-15.31513814558448</v>
+        <v>-6.907093284698876</v>
       </c>
       <c r="F84">
-        <v>-2.634565514500542</v>
+        <v>-0.2303832042118979</v>
       </c>
       <c r="G84">
-        <v>-8.736638479582487</v>
+        <v>-1.279560458845775</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.5323939387571607</v>
       </c>
       <c r="E85">
-        <v>-16.225823325475</v>
+        <v>-9.328654004034531</v>
       </c>
       <c r="F85">
-        <v>-2.903356654463134</v>
+        <v>-0.1824820307776136</v>
       </c>
       <c r="G85">
-        <v>-8.319457408071566</v>
+        <v>-0.8000919584719155</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5657257899394088</v>
       </c>
       <c r="E86">
-        <v>-17.10116376573566</v>
+        <v>-9.707945401494976</v>
       </c>
       <c r="F86">
-        <v>-2.852894997386797</v>
+        <v>-0.3991257859991711</v>
       </c>
       <c r="G86">
-        <v>-8.178932532345227</v>
+        <v>-0.2035199418630339</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6083213279576142</v>
       </c>
       <c r="E87">
-        <v>-17.99643854857808</v>
+        <v>-12.4363691050124</v>
       </c>
       <c r="F87">
-        <v>-3.126888284638969</v>
+        <v>-0.6993311029781287</v>
       </c>
       <c r="G87">
-        <v>-7.861254504624468</v>
+        <v>-0.8362214890629612</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6727588238430727</v>
       </c>
       <c r="E88">
-        <v>-19.34439317864925</v>
+        <v>-12.65269883683282</v>
       </c>
       <c r="F88">
-        <v>-3.145211771588895</v>
+        <v>-0.8150714248646785</v>
       </c>
       <c r="G88">
-        <v>-8.792842523674215</v>
+        <v>-1.145447090046591</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.7695452303447324</v>
       </c>
       <c r="E89">
-        <v>-19.88944936716047</v>
+        <v>-14.91232585412819</v>
       </c>
       <c r="F89">
-        <v>-3.078655764243566</v>
+        <v>-0.7738593182080002</v>
       </c>
       <c r="G89">
-        <v>-7.787715767034193</v>
+        <v>-1.183397698603128</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9072573490749282</v>
       </c>
       <c r="E90">
-        <v>-21.34554395653482</v>
+        <v>-16.82541139798658</v>
       </c>
       <c r="F90">
-        <v>-3.31761822239875</v>
+        <v>-1.273165225552028</v>
       </c>
       <c r="G90">
-        <v>-8.061838859774882</v>
+        <v>-0.8547964843109778</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.089044932212655</v>
       </c>
       <c r="E91">
-        <v>-22.73212194141741</v>
+        <v>-17.01917121535278</v>
       </c>
       <c r="F91">
-        <v>-3.304035482095047</v>
+        <v>-1.56373165943201</v>
       </c>
       <c r="G91">
-        <v>-8.201185776961381</v>
+        <v>-1.402009085001132</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.313043697593551</v>
       </c>
       <c r="E92">
-        <v>-24.58938045770924</v>
+        <v>-19.49674915816331</v>
       </c>
       <c r="F92">
-        <v>-3.469205315274046</v>
+        <v>-1.149198386988276</v>
       </c>
       <c r="G92">
-        <v>-8.373118505454725</v>
+        <v>-0.2428847569116922</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.572028121839689</v>
       </c>
       <c r="E93">
-        <v>-27.49912878896779</v>
+        <v>-23.13352587745731</v>
       </c>
       <c r="F93">
-        <v>-3.762861559566471</v>
+        <v>-0.8668708952965372</v>
       </c>
       <c r="G93">
-        <v>-8.343810634485765</v>
+        <v>-1.015720714472384</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.852885824513214</v>
       </c>
       <c r="E94">
-        <v>-28.36895807636112</v>
+        <v>-24.45250733082741</v>
       </c>
       <c r="F94">
-        <v>-3.431797900098426</v>
+        <v>-1.156674402798541</v>
       </c>
       <c r="G94">
-        <v>-8.669924682835855</v>
+        <v>-1.252546161746866</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.140875003762299</v>
       </c>
       <c r="E95">
-        <v>-30.24574563681103</v>
+        <v>-27.83803072675383</v>
       </c>
       <c r="F95">
-        <v>-3.620553838337335</v>
+        <v>-1.599402816531362</v>
       </c>
       <c r="G95">
-        <v>-8.920314700037082</v>
+        <v>-1.401050968305775</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.416106941891904</v>
       </c>
       <c r="E96">
-        <v>-32.3630336590973</v>
+        <v>-29.12203877536269</v>
       </c>
       <c r="F96">
-        <v>-3.894115546172649</v>
+        <v>-1.696767464321611</v>
       </c>
       <c r="G96">
-        <v>-8.7189428517124</v>
+        <v>-1.798708771537999</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.66181905884413</v>
       </c>
       <c r="E97">
-        <v>-35.00148337679333</v>
+        <v>-31.92208255954842</v>
       </c>
       <c r="F97">
-        <v>-4.134650245658348</v>
+        <v>-1.773794035638325</v>
       </c>
       <c r="G97">
-        <v>-8.928081351468288</v>
+        <v>-1.840705126277332</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.85815402649523</v>
       </c>
       <c r="E98">
-        <v>-37.56065762851107</v>
+        <v>-35.17879351232666</v>
       </c>
       <c r="F98">
-        <v>-3.959564026300435</v>
+        <v>-1.710100037669669</v>
       </c>
       <c r="G98">
-        <v>-9.084411871446472</v>
+        <v>-1.528378770920027</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.998226090651834</v>
       </c>
       <c r="E99">
-        <v>-40.33263845927127</v>
+        <v>-37.78918933354516</v>
       </c>
       <c r="F99">
-        <v>-3.868647390373579</v>
+        <v>-2.421797690356684</v>
       </c>
       <c r="G99">
-        <v>-9.361757123758537</v>
+        <v>-2.533876305596265</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.067607065395868</v>
       </c>
       <c r="E100">
-        <v>-42.43247827120599</v>
+        <v>-39.77132731330952</v>
       </c>
       <c r="F100">
-        <v>-3.930586077815703</v>
+        <v>-1.806703415816744</v>
       </c>
       <c r="G100">
-        <v>-9.73046470917178</v>
+        <v>-2.439199938720048</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.077383946365454</v>
       </c>
       <c r="E101">
-        <v>-44.5011372753609</v>
+        <v>-43.00414377298628</v>
       </c>
       <c r="F101">
-        <v>-4.132185852635018</v>
+        <v>-2.159926731677078</v>
       </c>
       <c r="G101">
-        <v>-9.952380285680144</v>
+        <v>-3.248818389962115</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.006771765982055</v>
       </c>
       <c r="E102">
-        <v>-47.42751416317562</v>
+        <v>-45.15909284935735</v>
       </c>
       <c r="F102">
-        <v>-3.970054471089489</v>
+        <v>-1.833746298048537</v>
       </c>
       <c r="G102">
-        <v>-10.12007695714025</v>
+        <v>-2.96007417395254</v>
       </c>
     </row>
   </sheetData>
